--- a/measurements/38/Filled_2D_sections/coronal/week38_coronal_Batch_Allmarks.xlsx
+++ b/measurements/38/Filled_2D_sections/coronal/week38_coronal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AK32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,122 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,43 +616,82 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.498810232004759</v>
+        <v>3620.748299319728</v>
       </c>
       <c r="D2" t="n">
-        <v>24.97529098173467</v>
+        <v>487.6128239291054</v>
       </c>
       <c r="E2" t="n">
-        <v>14.33690901500423</v>
+        <v>279.9110807691301</v>
       </c>
       <c r="F2" t="n">
         <v>1.742027584578858</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1913629960402298</v>
+        <v>0.1913629960402299</v>
       </c>
       <c r="H2" t="n">
+        <v>13</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.155877976190476</v>
+      </c>
+      <c r="J2" t="n">
+        <v>19.89583333333333</v>
+      </c>
+      <c r="K2" t="n">
+        <v>9.274696657509157</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P2" t="n">
+        <v>16.44159226190476</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>19.89583333333333</v>
+      </c>
+      <c r="R2" t="n">
+        <v>17.93433779761904</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W2" t="n">
+        <v>5.571056547619047</v>
+      </c>
+      <c r="X2" t="n">
+        <v>12.39025297619048</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.95712425595238</v>
+      </c>
+      <c r="Z2" t="n">
         <v>5</v>
       </c>
-      <c r="I2" t="n">
-        <v>0.6346227134146342</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.01905487804878</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.8617949695121953</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="AD2" t="n">
+        <v>2.155877976190476</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>4.172247023809524</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>3.401041666666667</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>9.524479476502083</v>
+      <c r="AK2" s="2" t="n">
+        <v>3630.532879818594</v>
       </c>
     </row>
     <row r="3">
@@ -553,17 +702,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.560380725758478</v>
+        <v>3644.21768707483</v>
       </c>
       <c r="D3" t="n">
-        <v>25.1714282995317</v>
+        <v>491.4421715622856</v>
       </c>
       <c r="E3" t="n">
-        <v>14.19648562408075</v>
+        <v>277.1694812320528</v>
       </c>
       <c r="F3" t="n">
         <v>1.773074616215913</v>
@@ -572,24 +721,63 @@
         <v>0.1896135341274323</v>
       </c>
       <c r="H3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.644345238095238</v>
+      </c>
+      <c r="J3" t="n">
+        <v>23.74813988095238</v>
+      </c>
+      <c r="K3" t="n">
+        <v>9.14720695970696</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>16.38578869047619</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>23.74813988095238</v>
+      </c>
+      <c r="R3" t="n">
+        <v>18.78580729166666</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="W3" t="n">
+        <v>4.566592261904762</v>
+      </c>
+      <c r="X3" t="n">
+        <v>11.80617559523809</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>7.033575148809525</v>
+      </c>
+      <c r="Z3" t="n">
         <v>5</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.6047065548780488</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.216368140243902</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.8907012195121951</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="AD3" t="n">
+        <v>1.644345238095238</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>4.157366071428571</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>3.127232142857143</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>23.03204194816147</v>
+      <c r="AK3" s="2" t="n">
+        <v>449.6731999402954</v>
       </c>
     </row>
     <row r="4">
@@ -600,43 +788,82 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.596073765615705</v>
+        <v>3657.8231292517</v>
       </c>
       <c r="D4" t="n">
-        <v>24.88364806407835</v>
+        <v>485.8236050605774</v>
       </c>
       <c r="E4" t="n">
-        <v>14.33690901500423</v>
+        <v>279.9110807691301</v>
       </c>
       <c r="F4" t="n">
         <v>1.73563548726134</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1947490469514445</v>
+        <v>0.1947490469514444</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I4" t="n">
-        <v>0.561547256097561</v>
+        <v>3.091517857142857</v>
       </c>
       <c r="J4" t="n">
-        <v>1.189596036585366</v>
+        <v>23.22544642857143</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8675114329268293</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>9.399646577380954</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>16.1328125</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>23.22544642857143</v>
+      </c>
+      <c r="R4" t="n">
+        <v>18.43052455357143</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="W4" t="n">
+        <v>4.242931547619047</v>
+      </c>
+      <c r="X4" t="n">
+        <v>10.96354166666667</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.420200892857142</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.091517857142857</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>3.705357142857143</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>3.348214285714286</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>14.49257940417383</v>
+      <c r="AK4" s="2" t="n">
+        <v>282.9503597957747</v>
       </c>
     </row>
     <row r="5">
@@ -647,43 +874,79 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9.625223081499108</v>
+        <v>3668.934240362812</v>
       </c>
       <c r="D5" t="n">
-        <v>24.99794786150863</v>
+        <v>488.055172534216</v>
       </c>
       <c r="E5" t="n">
-        <v>14.3048673577425</v>
+        <v>279.2855055559249</v>
       </c>
       <c r="F5" t="n">
-        <v>1.747513432760249</v>
+        <v>1.74751343276025</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1935583681628107</v>
+        <v>0.1935583681628108</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I5" t="n">
-        <v>0.520579268292683</v>
+        <v>2.485119047619047</v>
       </c>
       <c r="J5" t="n">
-        <v>1.192740091463415</v>
+        <v>23.28683035714285</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8526105182926831</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>8.644688644688644</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>15.29575892857143</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>23.28683035714285</v>
+      </c>
+      <c r="R5" t="n">
+        <v>18.26683407738095</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>10.16369047619048</v>
+      </c>
+      <c r="U5" t="n">
+        <v>6.739211309523809</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.485119047619047</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>4.153645833333333</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>3.201530612244898</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
-        <v>1.590638864428266</v>
+      <c r="AK5" s="2" t="n">
+        <v>1.590638864428267</v>
       </c>
     </row>
     <row r="6">
@@ -694,17 +957,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9.657346817370613</v>
+        <v>3681.179138321995</v>
       </c>
       <c r="D6" t="n">
-        <v>24.21399329639063</v>
+        <v>472.7493929295313</v>
       </c>
       <c r="E6" t="n">
-        <v>14.28466180475747</v>
+        <v>278.891016188122</v>
       </c>
       <c r="F6" t="n">
         <v>1.695104415305529</v>
@@ -713,23 +976,62 @@
         <v>0.2069830854220846</v>
       </c>
       <c r="H6" t="n">
+        <v>14</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J6" t="n">
+        <v>23.36681547619047</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7.817017431972787</v>
+      </c>
+      <c r="L6" t="n">
         <v>4</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.708079268292683</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.196836890243902</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.892482850609756</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="n">
+        <v>13.82440476190476</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>23.36681547619047</v>
+      </c>
+      <c r="R6" t="n">
+        <v>17.42466517857143</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>9.66703869047619</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6.631324404761904</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4.259672619047619</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>4.112723214285714</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.740221088435374</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AK6" s="2" t="n">
         <v>0.2301034144409848</v>
       </c>
     </row>
@@ -741,43 +1043,82 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9.636823319452708</v>
+        <v>3673.356009070294</v>
       </c>
       <c r="D7" t="n">
-        <v>24.24155288498576</v>
+        <v>473.2874610878172</v>
       </c>
       <c r="E7" t="n">
-        <v>14.27874374098894</v>
+        <v>278.7754730383555</v>
       </c>
       <c r="F7" t="n">
-        <v>1.697737092612518</v>
+        <v>1.697737092612519</v>
       </c>
       <c r="G7" t="n">
         <v>0.2060738510872483</v>
       </c>
       <c r="H7" t="n">
+        <v>13</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J7" t="n">
+        <v>23.49144345238095</v>
+      </c>
+      <c r="K7" t="n">
+        <v>8.477421016483516</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>12.74553571428571</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>23.49144345238095</v>
+      </c>
+      <c r="R7" t="n">
+        <v>17.07356770833333</v>
+      </c>
+      <c r="S7" t="n">
         <v>5</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.5317263719512195</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.203220274390244</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.8059451219512195</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="n">
+        <v>4.562872023809524</v>
+      </c>
+      <c r="X7" t="n">
+        <v>10.3813244047619</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>6.543526785714285</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>3.149181547619047</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.298642113095238</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>4</v>
+      <c r="AK7" s="2" t="n">
+        <v>11.9</v>
       </c>
     </row>
     <row r="8">
@@ -788,43 +1129,79 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9.597263533610946</v>
+        <v>3658.27664399093</v>
       </c>
       <c r="D8" t="n">
-        <v>25.20143921782331</v>
+        <v>492.0280990146455</v>
       </c>
       <c r="E8" t="n">
-        <v>14.31915483532882</v>
+        <v>279.5644515468961</v>
       </c>
       <c r="F8" t="n">
-        <v>1.759980914211868</v>
+        <v>1.759980914211867</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1898919689153853</v>
+        <v>0.1898919689153854</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5182926829268293</v>
+        <v>1.530877976190476</v>
       </c>
       <c r="J8" t="n">
-        <v>1.202553353658537</v>
+        <v>23.47842261904762</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8065548780487803</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>9.717106894841269</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>13.56770833333333</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>23.47842261904762</v>
+      </c>
+      <c r="R8" t="n">
+        <v>17.15401785714285</v>
+      </c>
+      <c r="S8" t="n">
+        <v>6</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4.626116071428571</v>
+      </c>
+      <c r="X8" t="n">
+        <v>10.11904761904762</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>7.181919642857142</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.366815476190476</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.530877976190476</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.6310642149390244</v>
+      <c r="AK8" s="2" t="n">
+        <v>1.937034970238095</v>
       </c>
     </row>
     <row r="9">
@@ -835,17 +1212,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9.508625817965497</v>
+        <v>3624.489795918367</v>
       </c>
       <c r="D9" t="n">
-        <v>24.97427558608171</v>
+        <v>487.5929995377858</v>
       </c>
       <c r="E9" t="n">
-        <v>14.4083464116585</v>
+        <v>281.3058108942849</v>
       </c>
       <c r="F9" t="n">
         <v>1.733320040519973</v>
@@ -854,24 +1231,57 @@
         <v>0.1915763179392612</v>
       </c>
       <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.203125</v>
+      </c>
+      <c r="J9" t="n">
+        <v>23.20870535714285</v>
+      </c>
+      <c r="K9" t="n">
+        <v>11.17615327380952</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>13.70535714285714</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>23.20870535714285</v>
+      </c>
+      <c r="R9" t="n">
+        <v>17.89853050595238</v>
+      </c>
+      <c r="S9" t="n">
         <v>5</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.5001905487804879</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.188738567073171</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.8334413109756097</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="n">
+        <v>4.767485119047619</v>
+      </c>
+      <c r="X9" t="n">
+        <v>9.765625</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>7.392857142857143</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.203125</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>1.038748094512195</v>
+      <c r="AK9" s="2" t="n">
+        <v>20.28031994047619</v>
       </c>
     </row>
     <row r="10">
@@ -882,17 +1292,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9.491969066032125</v>
+        <v>3618.140589569161</v>
       </c>
       <c r="D10" t="n">
-        <v>24.41401795643132</v>
+        <v>476.6546362922305</v>
       </c>
       <c r="E10" t="n">
-        <v>14.56897532939911</v>
+        <v>284.4418992882683</v>
       </c>
       <c r="F10" t="n">
         <v>1.67575395005067</v>
@@ -901,24 +1311,60 @@
         <v>0.200118693512602</v>
       </c>
       <c r="H10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.616443452380952</v>
+      </c>
+      <c r="J10" t="n">
+        <v>22.56138392857143</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9.882643398268398</v>
+      </c>
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.703125</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.155583079268293</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.9181592987804879</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="n">
+        <v>13.72767857142857</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>22.56138392857143</v>
+      </c>
+      <c r="R10" t="n">
+        <v>17.92596726190476</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>4.914434523809524</v>
+      </c>
+      <c r="X10" t="n">
+        <v>9.092261904761905</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>6.3046875</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.865327380952381</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.616443452380952</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.8401237773119918</v>
+      <c r="AK10" s="2" t="n">
+        <v>8.404541508838383</v>
       </c>
     </row>
     <row r="11">
@@ -929,17 +1375,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9.497917906008329</v>
+        <v>3620.408163265306</v>
       </c>
       <c r="D11" t="n">
-        <v>23.75966608233568</v>
+        <v>463.8791949408395</v>
       </c>
       <c r="E11" t="n">
-        <v>14.62612523683688</v>
+        <v>285.5576831953866</v>
       </c>
       <c r="F11" t="n">
         <v>1.624467567288113</v>
@@ -948,16 +1394,63 @@
         <v>0.2114256185958646</v>
       </c>
       <c r="H11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.828497023809524</v>
+      </c>
+      <c r="J11" t="n">
+        <v>18.91183035714286</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.774181547619047</v>
+      </c>
+      <c r="L11" t="n">
         <v>4</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.7201791158536586</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.9686547256097562</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.8765958460365854</v>
+      <c r="P11" t="n">
+        <v>14.06063988095238</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>18.91183035714286</v>
+      </c>
+      <c r="R11" t="n">
+        <v>17.11449032738095</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>9.092261904761905</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5.66220238095238</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.197172619047619</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.040178571428571</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.463541666666667</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.828497023809524</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AK11" s="2" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="12">
@@ -968,35 +1461,82 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9.525877453896491</v>
+        <v>3631.065759637188</v>
       </c>
       <c r="D12" t="n">
-        <v>23.95825473273673</v>
+        <v>467.7564019248599</v>
       </c>
       <c r="E12" t="n">
-        <v>14.77001535020224</v>
+        <v>288.3669663610912</v>
       </c>
       <c r="F12" t="n">
-        <v>1.622087327919309</v>
+        <v>1.62208732791931</v>
       </c>
       <c r="G12" t="n">
         <v>0.2085472646292978</v>
       </c>
       <c r="H12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.129836309523809</v>
+      </c>
+      <c r="J12" t="n">
+        <v>21.35044642857143</v>
+      </c>
+      <c r="K12" t="n">
+        <v>9.095474837662335</v>
+      </c>
+      <c r="L12" t="n">
         <v>4</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.7169397865853658</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.093559451219512</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.8865758384146341</v>
+      <c r="P12" t="n">
+        <v>13.99739583333333</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>21.35044642857143</v>
+      </c>
+      <c r="R12" t="n">
+        <v>17.30933779761904</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>4.306175595238095</v>
+      </c>
+      <c r="X12" t="n">
+        <v>8.175223214285714</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>5.648251488095237</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.671875</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.418154761904762</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.129836309523809</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK12" s="2" t="n">
+        <v>17.59254092261904</v>
       </c>
     </row>
     <row r="13">
@@ -1007,17 +1547,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9.636823319452708</v>
+        <v>3673.356009070294</v>
       </c>
       <c r="D13" t="n">
-        <v>21.75518399913136</v>
+        <v>424.7440685544695</v>
       </c>
       <c r="E13" t="n">
-        <v>14.80695970174743</v>
+        <v>289.0882608436403</v>
       </c>
       <c r="F13" t="n">
         <v>1.469253947963669</v>
@@ -1026,16 +1566,63 @@
         <v>0.2558693342897754</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5060022865853658</v>
+        <v>2.029389880952381</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8780487804878049</v>
+        <v>17.14285714285714</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7376857850609756</v>
+        <v>7.835159632034631</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="N13" t="n">
+        <v>16.63876488095238</v>
+      </c>
+      <c r="O13" t="n">
+        <v>13.94903273809524</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>4.410342261904762</v>
+      </c>
+      <c r="X13" t="n">
+        <v>9.879092261904761</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>6.300595238095238</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.816220238095238</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.107514880952381</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.029389880952381</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK13" s="2" t="n">
+        <v>17.07496279761904</v>
       </c>
     </row>
     <row r="14">
@@ -1046,17 +1633,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9.617787031528852</v>
+        <v>3666.09977324263</v>
       </c>
       <c r="D14" t="n">
-        <v>21.16981818036335</v>
+        <v>413.315497807094</v>
       </c>
       <c r="E14" t="n">
-        <v>14.8961512780771</v>
+        <v>290.8296201910291</v>
       </c>
       <c r="F14" t="n">
         <v>1.421160257114152</v>
@@ -1065,16 +1652,63 @@
         <v>0.2696812572028453</v>
       </c>
       <c r="H14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.393229166666667</v>
+      </c>
+      <c r="J14" t="n">
+        <v>16.88802083333333</v>
+      </c>
+      <c r="K14" t="n">
+        <v>7.499154491341992</v>
+      </c>
+      <c r="L14" t="n">
         <v>3</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.7029344512195123</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.8649961890243902</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.8071963922764228</v>
+      <c r="M14" t="n">
+        <v>16.88802083333333</v>
+      </c>
+      <c r="N14" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="O14" t="n">
+        <v>13.72395833333333</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>4.892113095238095</v>
+      </c>
+      <c r="X14" t="n">
+        <v>8.433779761904761</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>5.904389880952381</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.261904761904762</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.034970238095238</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.393229166666667</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK14" s="2" t="n">
+        <v>13.18452380952381</v>
       </c>
     </row>
     <row r="15">
@@ -1085,17 +1719,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9.596073765615705</v>
+        <v>3657.8231292517</v>
       </c>
       <c r="D15" t="n">
-        <v>21.06980587505713</v>
+        <v>411.3628766082582</v>
       </c>
       <c r="E15" t="n">
-        <v>14.72123485367473</v>
+        <v>287.4145852384113</v>
       </c>
       <c r="F15" t="n">
         <v>1.431252614640386</v>
@@ -1104,16 +1738,60 @@
         <v>0.2716329018394535</v>
       </c>
       <c r="H15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.046130952380952</v>
+      </c>
+      <c r="J15" t="n">
+        <v>17.40141369047619</v>
+      </c>
+      <c r="K15" t="n">
+        <v>7.991071428571426</v>
+      </c>
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.6574885670731707</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.8912919207317074</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.8121506605691057</v>
+      <c r="M15" t="n">
+        <v>17.40141369047619</v>
+      </c>
+      <c r="N15" t="n">
+        <v>17.33072916666666</v>
+      </c>
+      <c r="O15" t="n">
+        <v>12.83668154761905</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>4.713541666666666</v>
+      </c>
+      <c r="X15" t="n">
+        <v>8.095238095238095</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>5.618675595238095</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.202380952380952</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.046130952380952</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK15" s="2" t="n">
+        <v>14.47451636904762</v>
       </c>
     </row>
     <row r="16">
@@ -1124,35 +1802,79 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9.556513979773944</v>
+        <v>3642.743764172335</v>
       </c>
       <c r="D16" t="n">
-        <v>20.92244901017445</v>
+        <v>408.485909246263</v>
       </c>
       <c r="E16" t="n">
-        <v>14.65816690282124</v>
+        <v>286.1832585788908</v>
       </c>
       <c r="F16" t="n">
         <v>1.427357810078389</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2743369634339332</v>
+        <v>0.2743369634339333</v>
       </c>
       <c r="H16" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.328869047619047</v>
+      </c>
+      <c r="J16" t="n">
+        <v>17.65997023809524</v>
+      </c>
+      <c r="K16" t="n">
+        <v>8.063988095238095</v>
+      </c>
+      <c r="L16" t="n">
         <v>3</v>
       </c>
-      <c r="I16" t="n">
-        <v>0.6467225609756098</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.9045350609756098</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.8127858231707318</v>
+      <c r="M16" t="n">
+        <v>17.65997023809524</v>
+      </c>
+      <c r="N16" t="n">
+        <v>17.31956845238095</v>
+      </c>
+      <c r="O16" t="n">
+        <v>12.62648809523809</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>4.581473214285714</v>
+      </c>
+      <c r="X16" t="n">
+        <v>8.457961309523808</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>5.648809523809524</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.4609375</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.328869047619047</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK16" s="2" t="n">
+        <v>22.07217261904762</v>
       </c>
     </row>
     <row r="17">
@@ -1163,35 +1885,79 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9.515169541939322</v>
+        <v>3626.984126984127</v>
       </c>
       <c r="D17" t="n">
-        <v>20.85101164259562</v>
+        <v>407.0911796887715</v>
       </c>
       <c r="E17" t="n">
-        <v>14.63204329188277</v>
+        <v>285.6732261748541</v>
       </c>
       <c r="F17" t="n">
-        <v>1.425023916800661</v>
+        <v>1.42502391680066</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2750249747274846</v>
+        <v>0.2750249747274847</v>
       </c>
       <c r="H17" t="n">
+        <v>11</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.934523809523809</v>
+      </c>
+      <c r="J17" t="n">
+        <v>17.8125</v>
+      </c>
+      <c r="K17" t="n">
+        <v>7.535342261904762</v>
+      </c>
+      <c r="L17" t="n">
         <v>3</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.7123666158536586</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.9123475609756098</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.8252032520325203</v>
+      <c r="M17" t="n">
+        <v>17.8125</v>
+      </c>
+      <c r="N17" t="n">
+        <v>16.61272321428571</v>
+      </c>
+      <c r="O17" t="n">
+        <v>13.90811011904762</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6</v>
+      </c>
+      <c r="W17" t="n">
+        <v>4.263392857142857</v>
+      </c>
+      <c r="X17" t="n">
+        <v>7.619047619047619</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>5.036892361111112</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.399553571428571</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.934523809523809</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK17" s="2" t="n">
+        <v>17.6617916046627</v>
       </c>
     </row>
     <row r="18">
@@ -1202,17 +1968,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9.475609756097562</v>
+        <v>3611.904761904761</v>
       </c>
       <c r="D18" t="n">
-        <v>20.70712152341517</v>
+        <v>404.2818964095342</v>
       </c>
       <c r="E18" t="n">
-        <v>14.54040038876417</v>
+        <v>283.8840075901576</v>
       </c>
       <c r="F18" t="n">
         <v>1.42410944470389</v>
@@ -1221,16 +1987,63 @@
         <v>0.2777010782104273</v>
       </c>
       <c r="H18" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.77641369047619</v>
+      </c>
+      <c r="J18" t="n">
+        <v>17.88318452380952</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6.988467261904762</v>
+      </c>
+      <c r="L18" t="n">
         <v>3</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.6612995426829269</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.9159679878048781</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.8185022865853661</v>
+      <c r="M18" t="n">
+        <v>17.88318452380952</v>
+      </c>
+      <c r="N18" t="n">
+        <v>17.14657738095238</v>
+      </c>
+      <c r="O18" t="n">
+        <v>12.91108630952381</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4.402901785714286</v>
+      </c>
+      <c r="X18" t="n">
+        <v>8.431919642857142</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>5.573381696428571</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.77641369047619</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>3.841145833333333</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.725446428571428</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AK18" s="2" t="n">
+        <v>4.25</v>
       </c>
     </row>
     <row r="19">
@@ -1241,17 +2054,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9.430398572278406</v>
+        <v>3594.671201814059</v>
       </c>
       <c r="D19" t="n">
-        <v>20.23605547300199</v>
+        <v>395.0848925681341</v>
       </c>
       <c r="E19" t="n">
-        <v>14.53203097785392</v>
+        <v>283.7206048057193</v>
       </c>
       <c r="F19" t="n">
         <v>1.392513923472963</v>
@@ -1260,16 +2073,63 @@
         <v>0.2893931119169623</v>
       </c>
       <c r="H19" t="n">
+        <v>13</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.716889880952381</v>
+      </c>
+      <c r="J19" t="n">
+        <v>18.04315476190476</v>
+      </c>
+      <c r="K19" t="n">
+        <v>6.386790293040292</v>
+      </c>
+      <c r="L19" t="n">
         <v>3</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.6514862804878049</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.9241615853658537</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.8185022865853658</v>
+      <c r="M19" t="n">
+        <v>18.04315476190476</v>
+      </c>
+      <c r="N19" t="n">
+        <v>17.17819940476191</v>
+      </c>
+      <c r="O19" t="n">
+        <v>12.71949404761905</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>8.095238095238095</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4.70610119047619</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4.454985119047619</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.716889880952381</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>3.577008928571428</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.547300170068027</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK19" s="2" t="n">
+        <v>9.301339285714286</v>
       </c>
     </row>
     <row r="20">
@@ -1280,17 +2140,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9.353063652587746</v>
+        <v>3565.192743764172</v>
       </c>
       <c r="D20" t="n">
-        <v>20.3252470115336</v>
+        <v>396.8262511775607</v>
       </c>
       <c r="E20" t="n">
-        <v>14.47488107041615</v>
+        <v>282.604820898601</v>
       </c>
       <c r="F20" t="n">
         <v>1.404173679400687</v>
@@ -1299,16 +2159,63 @@
         <v>0.2845064321898413</v>
       </c>
       <c r="H20" t="n">
+        <v>14</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.902901785714286</v>
+      </c>
+      <c r="J20" t="n">
+        <v>17.90922619047619</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6.107833758503401</v>
+      </c>
+      <c r="L20" t="n">
         <v>3</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.6556783536585367</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.9173018292682927</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.8266323678861789</v>
+      <c r="M20" t="n">
+        <v>17.90922619047619</v>
+      </c>
+      <c r="N20" t="n">
+        <v>17.70647321428571</v>
+      </c>
+      <c r="O20" t="n">
+        <v>12.80133928571428</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>4.109002976190476</v>
+      </c>
+      <c r="X20" t="n">
+        <v>5.420386904761904</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>4.781901041666666</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.902901785714286</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>3.480282738095238</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.566432823129251</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK20" s="2" t="n">
+        <v>5.677455357142857</v>
       </c>
     </row>
     <row r="21">
@@ -1319,17 +2226,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9.111838191552648</v>
+        <v>3473.242630385487</v>
       </c>
       <c r="D21" t="n">
-        <v>22.81263128431832</v>
+        <v>445.3894679319291</v>
       </c>
       <c r="E21" t="n">
-        <v>14.15852589723541</v>
+        <v>276.4283627555484</v>
       </c>
       <c r="F21" t="n">
         <v>1.611229265666189</v>
@@ -1338,16 +2245,63 @@
         <v>0.2200214896253111</v>
       </c>
       <c r="H21" t="n">
+        <v>14</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.42671130952381</v>
+      </c>
+      <c r="J21" t="n">
+        <v>18.34077380952381</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7.276785714285714</v>
+      </c>
+      <c r="L21" t="n">
         <v>4</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.7073170731707318</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.9394054878048781</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.8514434070121951</v>
+      <c r="P21" t="n">
+        <v>13.80952380952381</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>18.34077380952381</v>
+      </c>
+      <c r="R21" t="n">
+        <v>16.62341889880952</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>9.488467261904761</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4.6484375</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.109002976190476</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.42671130952381</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>3.597470238095238</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.447916666666667</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK21" s="2" t="n">
+        <v>4.505208333333333</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2311,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK22" s="2" t="n">
+        <v>4.595362103174603</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2333,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK23" s="2" t="n">
+        <v>9.268725198412699</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2350,120 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK24" s="2" t="n">
+        <v>6.223119212962962</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AK25" s="2" t="n">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK26" s="2" t="n">
+        <v>3.028831845238095</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK27" s="2" t="n">
+        <v>2.164558531746032</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK28" s="2" t="n">
+        <v>1.845238095238095</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK29" s="2" t="n">
+        <v>1.869977678571428</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="n">
+        <v>3.794642857142857</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK31" s="2" t="n">
+        <v>2.840397799744898</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AK32" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/38/Filled_2D_sections/coronal/week38_coronal_Batch_Allmarks.xlsx
+++ b/measurements/38/Filled_2D_sections/coronal/week38_coronal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2469,4 +2675,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week38_coronal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>coronal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3630.532879818594</v>
+      </c>
+      <c r="D10" t="n">
+        <v>47.35743154288058</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3473.242630385487</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3681.179138321995</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>449.6731999402954</v>
+      </c>
+      <c r="D11" t="n">
+        <v>37.21554795282892</v>
+      </c>
+      <c r="E11" t="n">
+        <v>395.0848925681341</v>
+      </c>
+      <c r="F11" t="n">
+        <v>492.0280990146455</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.590638864428267</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1464958683762719</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.392513923472963</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.773074616215913</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.2301034144409848</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.03867766914105888</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1896135341274323</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2893931119169623</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis1_s00_idx0169.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>13</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis1_s01_idx0170.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>13</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>13</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis1_s02_idx0171.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>12</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis1_s03_idx0172.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>13</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>13</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis1_s04_idx0173.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>14</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis1_s05_idx0174.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>13</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>13</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis1_s06_idx0175.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>12</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>12</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis1_s07_idx0176.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis1_s08_idx0177.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>11</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>11</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis1_s09_idx0178.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>10</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis1_s10_idx0179.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>11</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>11</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis1_s11_idx0180.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>11</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>11</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis1_s12_idx0181.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>11</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>11</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis1_s13_idx0182.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>10</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>10</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis1_s14_idx0183.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis1_s15_idx0184.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>11</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>11</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis1_s16_idx0185.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>12</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>12</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis1_s17_idx0186.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>13</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>7</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>13</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>7</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis1_s18_idx0187.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>14</v>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>14</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis1_s19_idx0188.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>14</v>
+      </c>
+      <c r="C36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>7</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>14</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>7</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.410487037944882</v>
+      </c>
+      <c r="E40" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.5026246899500346</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.069923755276638</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.064104240533766</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>72</v>
+      </c>
+      <c r="C48" t="n">
+        <v>17.09141968419312</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2.85250273383283</v>
+      </c>
+      <c r="E48" t="n">
+        <v>12.62648809523809</v>
+      </c>
+      <c r="F48" t="n">
+        <v>23.74813988095238</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>85</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6.287683823529412</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.000385600868364</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.109002976190476</v>
+      </c>
+      <c r="F49" t="n">
+        <v>12.39025297619048</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>81</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.722594246031746</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.7301078275809014</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.172247023809524</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>